--- a/education_forms/040_master_program_evaluation_form--education_forms.xlsx
+++ b/education_forms/040_master_program_evaluation_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>master_program_evaluation_form</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>master_program_evaluation_form</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +543,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>program_title</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Program Title</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>accessing_information_satisfaction_level</t>
+          <t>program_duration</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>accessing_information_satisfaction_level</t>
+          <t>Program Duration</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>clarity_of_policies_satisfaction_level</t>
+          <t>satisfaction_with_program</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>clarity_of_policies_satisfaction_level</t>
+          <t>Satisfaction with Program</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>faculty_issues_and_academic_support_satisfaction_level</t>
+          <t>accessibility_of_program_resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>faculty_issues_and_academic_support_satisfaction_level</t>
+          <t>Accessibility of Program Resources</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>program_satisfaction</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Program Satisfaction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>faculty_satisfaction</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Faculty Satisfaction</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>academic_support_satisfaction</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Academic Support Satisfaction</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>accessibility_of_program_resources_satisfaction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Accessibility Of Program Resources Satisfaction</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>total_satisfaction</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Total Satisfaction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,306 +827,714 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>accessing_information_satisfaction_level_choices</t>
+          <t>satisfaction_with_program_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'highly_satisfied'}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Satisfied'}</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>accessing_information_satisfaction_level_choices</t>
+          <t>satisfaction_with_program_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'moderately_satisfied'}</t>
+          <t>moderately_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Moderately Satisfied'}</t>
+          <t>Moderately Satisfied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>accessing_information_satisfaction_level_choices</t>
+          <t>satisfaction_with_program_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>accessing_information_satisfaction_level_choices</t>
+          <t>satisfaction_with_program_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'neither_satisfied_nor_unsatisfied'}</t>
+          <t>neither_satisfied_nor_unsatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Satisfied nor Unsatisfied'}</t>
+          <t>Neither Satisfied nor Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>accessing_information_satisfaction_level_choices</t>
+          <t>satisfaction_with_program_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unsatisfied'}</t>
+          <t>somewhat_unsatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Unsatisfied'}</t>
+          <t>Somewhat Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>accessing_information_satisfaction_level_choices</t>
+          <t>satisfaction_with_program_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'highly_unsatisfied'}</t>
+          <t>highly_unsatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Unsatisfied'}</t>
+          <t>Highly Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>clarity_of_policies_satisfaction_level_choices</t>
+          <t>accessibility_of_program_resources_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'highly_satisfied'}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Satisfied'}</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>clarity_of_policies_satisfaction_level_choices</t>
+          <t>accessibility_of_program_resources_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'moderately_satisfied'}</t>
+          <t>moderately_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Moderately Satisfied'}</t>
+          <t>Moderately Satisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>clarity_of_policies_satisfaction_level_choices</t>
+          <t>accessibility_of_program_resources_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>clarity_of_policies_satisfaction_level_choices</t>
+          <t>accessibility_of_program_resources_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'neither_satisfied_nor_unsatisfied'}</t>
+          <t>neither_satisfied_nor_unsatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Satisfied nor Unsatisfied'}</t>
+          <t>Neither Satisfied nor Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>clarity_of_policies_satisfaction_level_choices</t>
+          <t>accessibility_of_program_resources_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unsatisfied'}</t>
+          <t>somewhat_unsatisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Unsatisfied'}</t>
+          <t>Somewhat Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>clarity_of_policies_satisfaction_level_choices</t>
+          <t>accessibility_of_program_resources_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'highly_unsatisfied'}</t>
+          <t>highly_unsatisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Unsatisfied'}</t>
+          <t>Highly Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>faculty_issues_and_academic_support_satisfaction_level_choices</t>
+          <t>program_satisfaction_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'highly_satisfied'}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Satisfied'}</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>faculty_issues_and_academic_support_satisfaction_level_choices</t>
+          <t>program_satisfaction_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'moderately_satisfied'}</t>
+          <t>moderately_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Moderately Satisfied'}</t>
+          <t>Moderately Satisfied</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>faculty_issues_and_academic_support_satisfaction_level_choices</t>
+          <t>program_satisfaction_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>faculty_issues_and_academic_support_satisfaction_level_choices</t>
+          <t>program_satisfaction_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'neither_satisfied_nor_unsatisfied'}</t>
+          <t>neither_satisfied_nor_unsatisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Satisfied nor Unsatisfied'}</t>
+          <t>Neither Satisfied nor Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>faculty_issues_and_academic_support_satisfaction_level_choices</t>
+          <t>program_satisfaction_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unsatisfied'}</t>
+          <t>somewhat_unsatisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Unsatisfied'}</t>
+          <t>Somewhat Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>faculty_issues_and_academic_support_satisfaction_level_choices</t>
+          <t>program_satisfaction_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'highly_unsatisfied'}</t>
+          <t>highly_unsatisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Unsatisfied'}</t>
+          <t>Highly Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>faculty_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>highly_satisfied</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Highly Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>faculty_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>moderately_satisfied</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Moderately Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>faculty_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>faculty_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>neither_satisfied_nor_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Neither Satisfied nor Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>faculty_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>somewhat_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Somewhat Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>faculty_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>highly_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Highly Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>academic_support_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>highly_satisfied</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Highly Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>academic_support_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>moderately_satisfied</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Moderately Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>academic_support_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>academic_support_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>neither_satisfied_nor_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Neither Satisfied nor Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>academic_support_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>somewhat_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Somewhat Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>academic_support_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>highly_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Highly Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>accessibility_of_program_resources_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>highly_satisfied</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Highly Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>accessibility_of_program_resources_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>moderately_satisfied</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Moderately Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>accessibility_of_program_resources_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>accessibility_of_program_resources_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>neither_satisfied_nor_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Neither Satisfied nor Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>accessibility_of_program_resources_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>somewhat_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Somewhat Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>accessibility_of_program_resources_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>highly_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Highly Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>total_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>highly_satisfied</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Highly Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>total_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>moderately_satisfied</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Moderately Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>total_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>total_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>neither_satisfied_nor_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Neither Satisfied nor Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>total_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>somewhat_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Somewhat Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>total_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>highly_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Highly Unsatisfied</t>
         </is>
       </c>
     </row>
